--- a/DateBase/orders/Dang Nguyen48_2026-10-15.xlsx
+++ b/DateBase/orders/Dang Nguyen48_2026-10-15.xlsx
@@ -523,6 +523,9 @@
       <c r="A11" t="str">
         <v>4</v>
       </c>
+      <c r="C11" t="str">
+        <v>321_雪柳叶_Spiraea  leaves_undefined_1bunch</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>

--- a/DateBase/orders/Dang Nguyen48_2026-10-15.xlsx
+++ b/DateBase/orders/Dang Nguyen48_2026-10-15.xlsx
@@ -526,6 +526,9 @@
       <c r="C11" t="str">
         <v>321_雪柳叶_Spiraea  leaves_undefined_1bunch</v>
       </c>
+      <c r="F11" t="str">
+        <v>100</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
@@ -584,7 +587,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>0351315207302020300</v>
+        <v>035131520730202030100</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Dang Nguyen48_2026-10-15.xlsx
+++ b/DateBase/orders/Dang Nguyen48_2026-10-15.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L11"/>
+  <dimension ref="A1:L41"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -530,9 +530,280 @@
         <v>100</v>
       </c>
     </row>
+    <row r="12">
+      <c r="C12" t="str">
+        <v>484_天鹅绒_Star of Bethlehem_undefined_1bunch</v>
+      </c>
+      <c r="F12" t="str">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="C13" t="str">
+        <v>741_袋鼠爪红_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F13" t="str">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="14" xml:space="preserve">
+      <c r="C14" t="str" xml:space="preserve">
+        <v xml:space="preserve">460_袋鼠爪黄_Kangaroo Paw
+red /green /orange / yellow_undefined_1bunch</v>
+      </c>
+      <c r="F14" t="str">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>5</v>
+      </c>
+      <c r="C15" t="str">
+        <v>197_粉红雪山_Sweet Avalanche_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F15" t="str">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="C16" t="str">
+        <v>181_月光女神_undefined_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F16" t="str">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>6</v>
+      </c>
+      <c r="C17" t="str">
+        <v>594_绿毛球_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F17" t="str">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>7</v>
+      </c>
+      <c r="C18" t="str">
+        <v>234_白泡泡_White Bubbles_Rosa rugosa Thunb._10stems</v>
+      </c>
+      <c r="F18" t="str">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="C19" t="str">
+        <v>277_草莓杏仁饼_undefined_Rosa rugosa Thunb._10stems</v>
+      </c>
+      <c r="F19" t="str">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="C20" t="str">
+        <v>225_果汁阳台_Juicy Terrazza_Rosa rugosa Thunb._10stems</v>
+      </c>
+      <c r="F20" t="str">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="C21" t="str">
+        <v>274_仙子之吻_undefined_Rosa rugosa Thunb._10stems</v>
+      </c>
+      <c r="F21" t="str">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>8</v>
+      </c>
+      <c r="C22" t="str">
+        <v>274_仙子之吻_undefined_Rosa rugosa Thunb._10stems</v>
+      </c>
+      <c r="F22" t="str">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="C23" t="str">
+        <v>286_红蕾丝_undefined_Rosa rugosa Thunb._10stems</v>
+      </c>
+      <c r="F23" t="str">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="C24" t="str">
+        <v>221_朱丽叶塔_Julieta_Rosa rugosa Thunb._10stems</v>
+      </c>
+      <c r="F24" t="str">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v/>
+      </c>
+      <c r="C25" t="str">
+        <v>279_完美甜蜜_undefined_Rosa rugosa Thunb._10stems</v>
+      </c>
+      <c r="F25" t="str">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>9</v>
+      </c>
+      <c r="C26" t="str">
+        <v>221_朱丽叶塔_Julieta_Rosa rugosa Thunb._10stems</v>
+      </c>
+      <c r="F26" t="str">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="C27" t="str">
+        <v>268_猩红泡泡_spray red_Rosa rugosa Thunb._10stems</v>
+      </c>
+      <c r="F27" t="str">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="C28" t="str">
+        <v>277_草莓杏仁饼_undefined_Rosa rugosa Thunb._10stems</v>
+      </c>
+      <c r="F28" t="str">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="C29" t="str">
+        <v>279_完美甜蜜_undefined_Rosa rugosa Thunb._10stems</v>
+      </c>
+      <c r="F29" t="str">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="C30" t="str">
+        <v>286_红蕾丝_undefined_Rosa rugosa Thunb._10stems</v>
+      </c>
+      <c r="F30" t="str">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="str">
+        <v>10</v>
+      </c>
+      <c r="C31" t="str">
+        <v>118_绣球老绿_Hydrangea Garden Lace_Hydrangea L._1stem</v>
+      </c>
+      <c r="F31" t="str">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="C32" t="str">
+        <v>126_绣球苹果绿_Hydrangea Garden Lace_Hydrangea L._1stem</v>
+      </c>
+      <c r="F32" t="str">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="str">
+        <v>11</v>
+      </c>
+      <c r="C33" t="str">
+        <v>126_绣球苹果绿_Hydrangea Garden Lace_Hydrangea L._1stem</v>
+      </c>
+      <c r="F33" t="str">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="C34" t="str">
+        <v>118_绣球老绿_Hydrangea Garden Lace_Hydrangea L._1stem</v>
+      </c>
+      <c r="F34" t="str">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="C35" t="str">
+        <v>123_绣球秋红_Hydrangea_Hydrangea L._1stem</v>
+      </c>
+      <c r="F35" t="str">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="C36" t="str">
+        <v>125_绣球蓝_Hydrangea Light Blue S_Hydrangea L._1stem</v>
+      </c>
+      <c r="F36" t="str">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="str">
+        <v>12</v>
+      </c>
+      <c r="C37" t="str">
+        <v>125_绣球蓝_Hydrangea Light Blue S_Hydrangea L._1stem</v>
+      </c>
+      <c r="F37" t="str">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="str">
+        <v>13</v>
+      </c>
+      <c r="C38" t="str">
+        <v>125_绣球蓝_Hydrangea Light Blue S_Hydrangea L._1stem</v>
+      </c>
+      <c r="F38" t="str">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="C39" t="str">
+        <v>106_绣球粉_Hydrangea Pink S_Hydrangea L._1stem</v>
+      </c>
+      <c r="F39" t="str">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="str">
+        <v>14</v>
+      </c>
+      <c r="C40" t="str">
+        <v>106_绣球粉_Hydrangea Pink S_Hydrangea L._1stem</v>
+      </c>
+      <c r="F40" t="str">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="str">
+        <v>15</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L11"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L41"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -587,7 +858,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>035131520730202030100</v>
+        <v>035131520730202030100301515304501861727819152378627825703025202512065551400</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Dang Nguyen48_2026-10-15.xlsx
+++ b/DateBase/orders/Dang Nguyen48_2026-10-15.xlsx
@@ -800,6 +800,9 @@
       <c r="A41" t="str">
         <v>15</v>
       </c>
+      <c r="C41" t="str">
+        <v>106_绣球粉_Hydrangea Pink S_Hydrangea L._1stem</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>

--- a/DateBase/orders/Dang Nguyen48_2026-10-15.xlsx
+++ b/DateBase/orders/Dang Nguyen48_2026-10-15.xlsx
@@ -803,6 +803,9 @@
       <c r="C41" t="str">
         <v>106_绣球粉_Hydrangea Pink S_Hydrangea L._1stem</v>
       </c>
+      <c r="F41" t="str">
+        <v>140</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
@@ -861,7 +864,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>035131520730202030100301515304501861727819152378627825703025202512065551400</v>
+        <v>03513152073020203010030151530450186172781915237862782570302520251206555140140</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Dang Nguyen48_2026-10-15.xlsx
+++ b/DateBase/orders/Dang Nguyen48_2026-10-15.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L41"/>
+  <dimension ref="A1:L81"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -807,9 +807,363 @@
         <v>140</v>
       </c>
     </row>
+    <row r="42">
+      <c r="A42" t="str">
+        <v>16</v>
+      </c>
+      <c r="C42" t="str">
+        <v>106_绣球粉_Hydrangea Pink S_Hydrangea L._1stem</v>
+      </c>
+      <c r="F42" t="str">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="C43" t="str">
+        <v>127_绣球孔雀粉_Hydrangea Peacoke_Hydrangea L._1stem</v>
+      </c>
+      <c r="F43" t="str">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="C44" t="str">
+        <v>114_绣球孔雀蓝_Hydrangea Peacoke_Hydrangea L._1stem</v>
+      </c>
+      <c r="F44" t="str">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="C45" t="str">
+        <v>100_绣球白_Hydrangea White S_Hydrangea L._1stem</v>
+      </c>
+      <c r="F45" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="str">
+        <v>17</v>
+      </c>
+      <c r="C46" t="str">
+        <v>225_果汁阳台_Juicy Terrazza_Rosa rugosa Thunb._10stems</v>
+      </c>
+      <c r="F46" t="str">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="C47" t="str">
+        <v>277_草莓杏仁饼_undefined_Rosa rugosa Thunb._10stems</v>
+      </c>
+      <c r="F47" t="str">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="C48" t="str">
+        <v>274_仙子之吻_undefined_Rosa rugosa Thunb._10stems</v>
+      </c>
+      <c r="F48" t="str">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="C49" t="str">
+        <v>268_猩红泡泡_spray red_Rosa rugosa Thunb._10stems</v>
+      </c>
+      <c r="F49" t="str">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="C50" t="str">
+        <v>234_白泡泡_White Bubbles_Rosa rugosa Thunb._10stems</v>
+      </c>
+      <c r="F50" t="str">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="C51" t="str">
+        <v>138_卡罗拉_Carola_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F51" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="str">
+        <v>18</v>
+      </c>
+      <c r="C52" t="str">
+        <v>137_凯瑟琳_Catherine_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F52" t="str">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="C53" t="str">
+        <v>181_月光女神_undefined_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F53" t="str">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="str">
+        <v>19</v>
+      </c>
+      <c r="C54" t="str">
+        <v>137_凯瑟琳_Catherine_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F54" t="str">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="C55" t="str">
+        <v>138_卡罗拉_Carola_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F55" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="C56" t="str">
+        <v>574_迷你菊白_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F56" t="str">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="C57" t="str">
+        <v>576_迷你菊紫_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F57" t="str">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="str">
+        <v>20</v>
+      </c>
+      <c r="C58" t="str">
+        <v>688_山归来橙_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F58" t="str">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="59" xml:space="preserve">
+      <c r="C59" t="str" xml:space="preserve">
+        <v xml:space="preserve">542_吊米 红_hanging amaranthus
+red_undefined_1bunch</v>
+      </c>
+      <c r="F59" t="str">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="C60" t="str">
+        <v>576_迷你菊紫_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F60" t="str">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="C61" t="str">
+        <v>575_迷你菊深粉_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F61" t="str">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="C62" t="str">
+        <v>846_玛格丽特_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F62" t="str">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="C63" t="str">
+        <v>878_玛格丽特粉_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F63" t="str">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="str">
+        <v>21</v>
+      </c>
+      <c r="C64" t="str">
+        <v>155_曼塔_Menta_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F64" t="str">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="C65" t="str">
+        <v>149_骄傲_Proud_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F65" t="str">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="str">
+        <v>22</v>
+      </c>
+      <c r="C66" t="str">
+        <v>149_骄傲_Proud_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F66" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="C67" t="str">
+        <v>135_甜蜜曼塔_sweet menta_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F67" t="str">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="str">
+        <v>23</v>
+      </c>
+      <c r="C68" t="str">
+        <v>175_火灵鸟_Free Spirit_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F68" t="str">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="C69" t="str">
+        <v>208_紫霞仙子 _Nightingale_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F69" t="str">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="str">
+        <v>24</v>
+      </c>
+      <c r="C70" t="str">
+        <v>208_紫霞仙子 _Nightingale_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F70" t="str">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="C71" t="str">
+        <v>184_微光_shimmer_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F71" t="str">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="C72" t="str">
+        <v>211_海洋之心_Nautica_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F72" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="C73" t="str">
+        <v>284_可爱瓷_undefined_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F73" t="str">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="str">
+        <v>25</v>
+      </c>
+      <c r="C74" t="str">
+        <v>284_可爱瓷_undefined_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F74" t="str">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="C75" t="str">
+        <v>181_月光女神_undefined_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F75" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="C76" t="str">
+        <v>209_海洋之歌_Ocean Song_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F76" t="str">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="str">
+        <v>26</v>
+      </c>
+      <c r="C77" t="str">
+        <v>209_海洋之歌_Ocean Song_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F77" t="str">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="C78" t="str">
+        <v>195_闺蜜_Alter Ego_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F78" t="str">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="C79" t="str">
+        <v>193_粉爱神_Pink Cupid_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F79" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="str">
+        <v>27</v>
+      </c>
+      <c r="C80" t="str">
+        <v>193_粉爱神_Pink Cupid_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F80" t="str">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="C81" t="str">
+        <v>203_佛罗伊德_Floyd_Rosa rugosa Thunb._20stems</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L41"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L81"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -864,7 +1218,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>03513152073020203010030151530450186172781915237862782570302520251206555140140</v>
+        <v>03513152073020203010030151530450186172781915237862782570302520251206555140140505051103212182102116111030222015820593020211033281822610181024111910210</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Dang Nguyen48_2026-10-15.xlsx
+++ b/DateBase/orders/Dang Nguyen48_2026-10-15.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L81"/>
+  <dimension ref="A1:L131"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1160,10 +1160,461 @@
       <c r="C81" t="str">
         <v>203_佛罗伊德_Floyd_Rosa rugosa Thunb._20stems</v>
       </c>
+      <c r="F81" t="str">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="str">
+        <v>28</v>
+      </c>
+      <c r="C82" t="str">
+        <v>203_佛罗伊德_Floyd_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F82" t="str">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="C83" t="str">
+        <v>154_莫泊_Moab_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F83" t="str">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="str">
+        <v>29</v>
+      </c>
+      <c r="C84" t="str">
+        <v>154_莫泊_Moab_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F84" t="str">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="C85" t="str">
+        <v>177_国王日_Kings Day_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F85" t="str">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="C86" t="str">
+        <v>277_草莓杏仁饼_undefined_Rosa rugosa Thunb._10stems</v>
+      </c>
+      <c r="F86" t="str">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="C87" t="str">
+        <v>224_折射_Reflex_Rosa rugosa Thunb._10stems</v>
+      </c>
+      <c r="F87" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="C88" t="str">
+        <v>285_多头紫罗兰_undefined_Rosa rugosa Thunb._10stems</v>
+      </c>
+      <c r="F88" t="str">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="str">
+        <v>30</v>
+      </c>
+      <c r="C89" t="str">
+        <v>100_绣球白_Hydrangea White S_Hydrangea L._1stem</v>
+      </c>
+      <c r="F89" t="str">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="90" xml:space="preserve">
+      <c r="C90" t="str" xml:space="preserve">
+        <v xml:space="preserve">349_千层金绿_Melaleuca bracteata
+（dyed orange）_Melaleuca bracteata F.Muell._1bunch</v>
+      </c>
+      <c r="F90" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="91" xml:space="preserve">
+      <c r="C91" t="str" xml:space="preserve">
+        <v xml:space="preserve">350_千层金红_Melaleuca bracteata
+（dyed red）_Melaleuca bracteata F.Muell._1bunch</v>
+      </c>
+      <c r="F91" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="92" xml:space="preserve">
+      <c r="C92" t="str" xml:space="preserve">
+        <v xml:space="preserve">351_千层金橙_Melaleuca bracteata
+（dyed orange）_Melaleuca bracteata F.Muell._1bunch</v>
+      </c>
+      <c r="F92" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="str">
+        <v/>
+      </c>
+      <c r="C93" t="str">
+        <v>741_袋鼠爪红_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F93" t="str">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="C94" t="str">
+        <v>411_紫罗兰白_violet white_undefined_1bunch</v>
+      </c>
+      <c r="F94" t="str">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="str">
+        <v>31</v>
+      </c>
+      <c r="C95" t="str">
+        <v>411_紫罗兰白_violet white_undefined_1bunch</v>
+      </c>
+      <c r="F95" t="str">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="C96" t="str">
+        <v>412_紫罗兰粉_violet pink_undefined_1bunch</v>
+      </c>
+      <c r="F96" t="str">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="str">
+        <v>32</v>
+      </c>
+      <c r="C97" t="str">
+        <v>1_白洋桔梗_White Lisianthus_Eustoma grandiflorum (Raf.) Shinners_800/600g</v>
+      </c>
+      <c r="F97" t="str">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="C98" t="str">
+        <v>11_香槟洋桔梗_Champagne Lisianthus_Eustoma grandiflorum (Raf.) Shinners_800/600g</v>
+      </c>
+      <c r="F98" t="str">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="C99" t="str">
+        <v>14_波浪浅紫洋桔梗_Wavy Light Purple Lisianthus_Eustoma grandiflorum (Raf.) Shinners_800/600g</v>
+      </c>
+      <c r="F99" t="str">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="str">
+        <v>33</v>
+      </c>
+      <c r="C100" t="str">
+        <v>14_波浪浅紫洋桔梗_Wavy Light Purple Lisianthus_Eustoma grandiflorum (Raf.) Shinners_800/600g</v>
+      </c>
+      <c r="F100" t="str">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="str">
+        <v/>
+      </c>
+      <c r="C101" t="str">
+        <v>9_茶色洋桔梗_Tea Color Lisianthus_Eustoma grandiflorum (Raf.) Shinners_800/600g</v>
+      </c>
+      <c r="F101" t="str">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="C102" t="str">
+        <v>3_波浪白洋桔梗_Wavy White Lisianthus_Eustoma grandiflorum (Raf.) Shinners_800/600g</v>
+      </c>
+      <c r="F102" t="str">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="C103" t="str">
+        <v>2_粉洋桔梗_Pink Lisianthus_Eustoma grandiflorum (Raf.) Shinners_800/600g</v>
+      </c>
+      <c r="F103" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="str">
+        <v>34</v>
+      </c>
+      <c r="C104" t="str">
+        <v>2_粉洋桔梗_Pink Lisianthus_Eustoma grandiflorum (Raf.) Shinners_800/600g</v>
+      </c>
+      <c r="F104" t="str">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="C105" t="str">
+        <v>7_翠绿洋桔梗_Dark Green Lisianthus_Eustoma grandiflorum (Raf.) Shinners_800/600g</v>
+      </c>
+      <c r="F105" t="str">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="C106" t="str">
+        <v>12_肉粉洋桔梗_Peach Lisianthus_Eustoma grandiflorum (Raf.) Shinners_800/600g</v>
+      </c>
+      <c r="F106" t="str">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="str">
+        <v>35</v>
+      </c>
+      <c r="C107" t="str">
+        <v>12_肉粉洋桔梗_Peach Lisianthus_Eustoma grandiflorum (Raf.) Shinners_800/600g</v>
+      </c>
+      <c r="F107" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="C108" t="str">
+        <v>900_紫罗兰深紫_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F108" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="C109" t="str">
+        <v>899_紫罗兰浅黄_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F109" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="C110" t="str">
+        <v>505_紫罗兰紫_violet purple_undefined_1bunch</v>
+      </c>
+      <c r="F110" t="str">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="C111" t="str">
+        <v>285_多头紫罗兰_undefined_Rosa rugosa Thunb._10stems</v>
+      </c>
+      <c r="F111" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="C112" t="str">
+        <v>506_紫罗兰香槟色_violet champagne_undefined_1bunch</v>
+      </c>
+      <c r="F112" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="C113" t="str">
+        <v>412_紫罗兰粉_violet pink_undefined_1bunch</v>
+      </c>
+      <c r="F113" t="str">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="str">
+        <v>36</v>
+      </c>
+      <c r="C114" t="str">
+        <v>100_绣球白_Hydrangea White S_Hydrangea L._1stem</v>
+      </c>
+      <c r="F114" t="str">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="115" xml:space="preserve">
+      <c r="C115" t="str" xml:space="preserve">
+        <v xml:space="preserve">414_风铃花粉色_Canterbury Bells
+pink_undefined_1bunch</v>
+      </c>
+      <c r="F115" t="str">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="116" xml:space="preserve">
+      <c r="C116" t="str" xml:space="preserve">
+        <v xml:space="preserve">413_风铃花淡紫色_Canterbury Bells
+light purple_undefined_1bunch</v>
+      </c>
+      <c r="F116" t="str">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="117" xml:space="preserve">
+      <c r="C117" t="str" xml:space="preserve">
+        <v xml:space="preserve">508_风铃花白色_Canterbury Bells 
+white_undefined_1bunch</v>
+      </c>
+      <c r="F117" t="str">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="C118" t="str">
+        <v>412_紫罗兰粉_violet pink_undefined_1bunch</v>
+      </c>
+      <c r="F118" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="str">
+        <v>37</v>
+      </c>
+      <c r="C119" t="str">
+        <v>284_可爱瓷_undefined_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F119" t="str">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="C120" t="str">
+        <v>157_流沙_Quicksand_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F120" t="str">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="C121" t="str">
+        <v>152_白荔枝_White Ohara_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F121" t="str">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="str">
+        <v>38</v>
+      </c>
+      <c r="C122" t="str">
+        <v>152_白荔枝_White Ohara_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F122" t="str">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="C123" t="str">
+        <v>189_洛神_Mandala_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F123" t="str">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="str">
+        <v>39</v>
+      </c>
+      <c r="C124" t="str">
+        <v>189_洛神_Mandala_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F124" t="str">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="C125" t="str">
+        <v>277_草莓杏仁饼_undefined_Rosa rugosa Thunb._10stems</v>
+      </c>
+      <c r="F125" t="str">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="C126" t="str">
+        <v>281_莱拉_undefined_Rosa rugosa Thunb._10stems</v>
+      </c>
+      <c r="F126" t="str">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="C127" t="str">
+        <v>286_红蕾丝_undefined_Rosa rugosa Thunb._10stems</v>
+      </c>
+      <c r="F127" t="str">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="str">
+        <v>40</v>
+      </c>
+      <c r="C128" t="str">
+        <v>144_高原红_High Plateau Red_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F128" t="str">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="C129" t="str">
+        <v>412_紫罗兰粉_violet pink_undefined_1bunch</v>
+      </c>
+      <c r="F129" t="str">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="C130" t="str">
+        <v>334_狗尾草_puppy tail grass_undefined_1bunch</v>
+      </c>
+      <c r="F130" t="str">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="C131" t="str">
+        <v>333_狼尾草_wolf tail grass_undefined_1bunch</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L81"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L131"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -1218,7 +1669,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>03513152073020203010030151530450186172781915237862782570302520251206555140140505051103212182102116111030222015820593020211033281822610181024111910210</v>
+        <v>03513152073020203010030151530450186172781915237862782570302520251206555140140505051103212182102116111030222015820593020211033281822610181024111910211531777171020401010101540606030301515302051520401010102010104067402040107333301721312182020200</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Dang Nguyen48_2026-10-15.xlsx
+++ b/DateBase/orders/Dang Nguyen48_2026-10-15.xlsx
@@ -1611,6 +1611,9 @@
       <c r="C131" t="str">
         <v>333_狼尾草_wolf tail grass_undefined_1bunch</v>
       </c>
+      <c r="F131" t="str">
+        <v>20</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
@@ -1669,7 +1672,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>03513152073020203010030151530450186172781915237862782570302520251206555140140505051103212182102116111030222015820593020211033281822610181024111910211531777171020401010101540606030301515302051520401010102010104067402040107333301721312182020200</v>
+        <v>035131520730202030100301515304501861727819152378627825703025202512065551401405050511032121821021161110302220158205930202110332818226101810241119102115317771710204010101015406060303015153020515204010101020101040674020401073333017213121820202020</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Dang Nguyen48_2026-10-15.xlsx
+++ b/DateBase/orders/Dang Nguyen48_2026-10-15.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L131"/>
+  <dimension ref="A1:L141"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1615,9 +1615,98 @@
         <v>20</v>
       </c>
     </row>
+    <row r="132">
+      <c r="A132" t="str">
+        <v>41</v>
+      </c>
+      <c r="C132" t="str">
+        <v>273_蓝调_bluetone_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F132" t="str">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="C133" t="str">
+        <v>192_粉荔枝_Pink Ohara_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F133" t="str">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="str">
+        <v>42</v>
+      </c>
+      <c r="C134" t="str">
+        <v>192_粉荔枝_Pink Ohara_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F134" t="str">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="str">
+        <v>43</v>
+      </c>
+      <c r="C135" t="str">
+        <v>192_粉荔枝_Pink Ohara_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F135" t="str">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="C136" t="str">
+        <v>284_可爱瓷_undefined_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F136" t="str">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="C137" t="str">
+        <v>286_红蕾丝_undefined_Rosa rugosa Thunb._10stems</v>
+      </c>
+      <c r="F137" t="str">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="C138" t="str">
+        <v>268_猩红泡泡_spray red_Rosa rugosa Thunb._10stems</v>
+      </c>
+      <c r="F138" t="str">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="str">
+        <v>44</v>
+      </c>
+      <c r="C139" t="str">
+        <v>170_奶油杯_Butter Cup_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F139" t="str">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="C140" t="str">
+        <v>160_卡布奇诺_Cappuccino_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F140" t="str">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="str">
+        <v>45</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L131"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L141"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -1672,7 +1761,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>035131520730202030100301515304501861727819152378627825703025202512065551401405050511032121821021161110302220158205930202110332818226101810241119102115317771710204010101015406060303015153020515204010101020101040674020401073333017213121820202020</v>
+        <v>03513152073020203010030151530450186172781915237862782570302520251206555140140505051103212182102116111030222015820593020211033281822610181024111910211531777171020401010101540606030301515302051520401010102010104067402040107333301721312182020202017274432261124170</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Dang Nguyen48_2026-10-15.xlsx
+++ b/DateBase/orders/Dang Nguyen48_2026-10-15.xlsx
@@ -1703,6 +1703,12 @@
       <c r="A141" t="str">
         <v>45</v>
       </c>
+      <c r="C141" t="str">
+        <v>160_卡布奇诺_Cappuccino_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F141" t="str">
+        <v>11</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
@@ -1761,7 +1767,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>03513152073020203010030151530450186172781915237862782570302520251206555140140505051103212182102116111030222015820593020211033281822610181024111910211531777171020401010101540606030301515302051520401010102010104067402040107333301721312182020202017274432261124170</v>
+        <v>035131520730202030100301515304501861727819152378627825703025202512065551401405050511032121821021161110302220158205930202110332818226101810241119102115317771710204010101015406060303015153020515204010101020101040674020401073333017213121820202020172744322611241711</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Dang Nguyen48_2026-10-15.xlsx
+++ b/DateBase/orders/Dang Nguyen48_2026-10-15.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L141"/>
+  <dimension ref="A1:L151"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1710,9 +1710,98 @@
         <v>11</v>
       </c>
     </row>
+    <row r="142">
+      <c r="C142" t="str">
+        <v>268_猩红泡泡_spray red_Rosa rugosa Thunb._10stems</v>
+      </c>
+      <c r="F142" t="str">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="C143" t="str">
+        <v>436_木百合_leucadendron _undefined_1bunch</v>
+      </c>
+      <c r="F143" t="str">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="C144" t="str">
+        <v>221_朱丽叶塔_Julieta_Rosa rugosa Thunb._10stems</v>
+      </c>
+      <c r="F144" t="str">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="str">
+        <v>46</v>
+      </c>
+      <c r="C145" t="str">
+        <v>649_洋牡丹樱花粉_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F145" t="str">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="str">
+        <v>47</v>
+      </c>
+      <c r="C146" t="str">
+        <v>246_多头蓝莓_Blueberry Spray_Rosa rugosa Thunb._10stems</v>
+      </c>
+      <c r="F146" t="str">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="C147" t="str">
+        <v>268_猩红泡泡_spray red_Rosa rugosa Thunb._10stems</v>
+      </c>
+      <c r="F147" t="str">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="C148" t="str">
+        <v>229_黄蝴蝶_Yellow Butterfly_Rosa rugosa Thunb._10stems</v>
+      </c>
+      <c r="F148" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="str">
+        <v>48</v>
+      </c>
+      <c r="C149" t="str">
+        <v>144_高原红_High Plateau Red_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F149" t="str">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="C150" t="str">
+        <v>274_仙子之吻_undefined_Rosa rugosa Thunb._10stems</v>
+      </c>
+      <c r="F150" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="C151" t="str">
+        <v>177_国王日_Kings Day_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F151" t="str">
+        <v>5</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L141"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L151"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -1767,7 +1856,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>035131520730202030100301515304501861727819152378627825703025202512065551401405050511032121821021161110302220158205930202110332818226101810241119102115317771710204010101015406060303015153020515204010101020101040674020401073333017213121820202020172744322611241711</v>
+        <v>03513152073020203010030151530450186172781915237862782570302520251206555140140505051103212182102116111030222015820593020211033281822610181024111910211531777171020401010101540606030301515302051520401010102010104067402040107333301721312182020202017274432261124171131528501520103055</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Dang Nguyen48_2026-10-15.xlsx
+++ b/DateBase/orders/Dang Nguyen48_2026-10-15.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L151"/>
+  <dimension ref="A1:L153"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1799,9 +1799,28 @@
         <v>5</v>
       </c>
     </row>
+    <row r="152">
+      <c r="A152" t="str">
+        <v>49</v>
+      </c>
+      <c r="C152" t="str">
+        <v>244_繁星_undefined_Rosa rugosa Thunb._10stems</v>
+      </c>
+      <c r="F152" t="str">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="C153" t="str">
+        <v>648_洋牡丹河内_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F153" t="str">
+        <v>29</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L151"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L153"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -1856,7 +1875,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>03513152073020203010030151530450186172781915237862782570302520251206555140140505051103212182102116111030222015820593020211033281822610181024111910211531777171020401010101540606030301515302051520401010102010104067402040107333301721312182020202017274432261124171131528501520103055</v>
+        <v>035131520730202030100301515304501861727819152378627825703025202512065551401405050511032121821021161110302220158205930202110332818226101810241119102115317771710204010101015406060303015153020515204010101020101040674020401073333017213121820202020172744322611241711315285015201030554029</v>
       </c>
     </row>
   </sheetData>
